--- a/data/trans_dic/P32-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensa que debería beber menos</t>
+          <t>Población que piensa que debería beber menos (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,79</t>
+          <t>1,73; 4,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 9,0</t>
+          <t>4,2; 8,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,31</t>
+          <t>3,18; 8,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 12,26</t>
+          <t>5,0; 11,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 6,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,6</t>
+          <t>0,43; 3,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,49</t>
+          <t>1,52; 4,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,66</t>
+          <t>3,19; 6,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,33</t>
+          <t>2,53; 6,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,74</t>
+          <t>4,24; 9,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,81</t>
+          <t>1,97; 3,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,81</t>
+          <t>5,74; 8,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,4</t>
+          <t>3,98; 6,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,03</t>
+          <t>4,16; 8,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,06</t>
+          <t>0,89; 3,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,0</t>
+          <t>1,3; 3,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,15</t>
+          <t>2,46; 5,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,67</t>
+          <t>0,8; 3,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,3</t>
+          <t>1,75; 3,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,78</t>
+          <t>4,61; 6,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 5,74</t>
+          <t>3,67; 5,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,48</t>
+          <t>2,78; 5,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,42</t>
+          <t>0,87; 4,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,7</t>
+          <t>3,48; 9,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,97</t>
+          <t>3,56; 8,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,45</t>
+          <t>4,17; 9,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,51</t>
+          <t>0,8; 6,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,83</t>
+          <t>1,69; 6,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,21</t>
+          <t>1,95; 7,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,21</t>
+          <t>0,65; 3,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,05</t>
+          <t>2,88; 6,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,75</t>
+          <t>3,21; 6,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,73</t>
+          <t>3,66; 7,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,7</t>
+          <t>2,07; 3,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,05</t>
+          <t>5,73; 8,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,44</t>
+          <t>4,23; 6,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,67</t>
+          <t>5,01; 7,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,54</t>
+          <t>0,79; 2,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,34</t>
+          <t>1,32; 3,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,38</t>
+          <t>2,28; 4,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,56</t>
+          <t>1,21; 3,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,96</t>
+          <t>1,83; 3,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,13</t>
+          <t>4,4; 6,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,36</t>
+          <t>3,84; 5,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,79</t>
+          <t>3,48; 5,85</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensa que debería beber menos</t>
+          <t>Población que piensa que debería beber menos (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7719; 22544</t>
+          <t>8145; 23508</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22246; 46042</t>
+          <t>21491; 45405</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11705; 29680</t>
+          <t>11344; 29892</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12701; 29919</t>
+          <t>12188; 29012</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 11117</t>
+          <t>0; 11058</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>982; 8259</t>
+          <t>991; 8976</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6049</t>
+          <t>0; 5482</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2606</t>
+          <t>0; 2935</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10250; 28662</t>
+          <t>9691; 28513</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23442; 49315</t>
+          <t>23598; 49226</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12051; 31154</t>
+          <t>12455; 31297</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13455; 30305</t>
+          <t>13190; 30354</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19674; 40386</t>
+          <t>20836; 41199</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69621; 105466</t>
+          <t>68732; 106096</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48641; 80174</t>
+          <t>49918; 82047</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41345; 79135</t>
+          <t>40980; 79643</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4274; 16359</t>
+          <t>4772; 17439</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7697; 23867</t>
+          <t>7736; 23116</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16941; 37459</t>
+          <t>17883; 39007</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5569; 25969</t>
+          <t>5684; 26820</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28556; 52595</t>
+          <t>27851; 52465</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81005; 121671</t>
+          <t>82774; 122306</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72905; 113740</t>
+          <t>72668; 110002</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43139; 92842</t>
+          <t>47026; 96203</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2614; 15509</t>
+          <t>3060; 16371</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11817; 31656</t>
+          <t>11343; 31021</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13703; 34018</t>
+          <t>13500; 33963</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14165; 32532</t>
+          <t>14368; 32574</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5150</t>
+          <t>0; 5321</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1797; 14626</t>
+          <t>1795; 14120</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4265; 19287</t>
+          <t>4768; 17909</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4470; 17750</t>
+          <t>4804; 17414</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3961; 17471</t>
+          <t>3537; 17042</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15393; 38833</t>
+          <t>15840; 38443</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21876; 44650</t>
+          <t>21240; 44682</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22463; 45640</t>
+          <t>21596; 43881</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39191; 69535</t>
+          <t>38924; 66093</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115136; 163765</t>
+          <t>116677; 164265</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86101; 128036</t>
+          <t>84063; 125061</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76584; 120680</t>
+          <t>78868; 122793</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6959; 22689</t>
+          <t>7108; 22856</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14266; 35088</t>
+          <t>13863; 34593</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26470; 50088</t>
+          <t>26133; 50483</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11159; 36355</t>
+          <t>12351; 37393</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50238; 82102</t>
+          <t>50788; 83364</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>135448; 189165</t>
+          <t>135743; 187385</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>119857; 168065</t>
+          <t>120345; 167765</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>91466; 150336</t>
+          <t>90399; 151778</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,99</t>
+          <t>1,6; 5,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,87</t>
+          <t>3,96; 8,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,37</t>
+          <t>3,14; 8,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,89</t>
+          <t>5,37; 12,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>0,0; 6,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,92</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,47</t>
+          <t>1,64; 4,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,65</t>
+          <t>3,33; 6,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,36</t>
+          <t>2,61; 6,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,75</t>
+          <t>4,4; 9,57</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,89</t>
+          <t>1,97; 3,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 8,86</t>
+          <t>5,68; 8,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,55</t>
+          <t>3,96; 6,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,09</t>
+          <t>4,52; 8,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,27</t>
+          <t>0,74; 3,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,87</t>
+          <t>1,32; 4,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,37</t>
+          <t>2,35; 5,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,79</t>
+          <t>2,02; 5,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,29</t>
+          <t>1,75; 3,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,82</t>
+          <t>4,55; 6,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 5,56</t>
+          <t>3,56; 5,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,68</t>
+          <t>3,84; 6,37</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,67</t>
+          <t>0,88; 4,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 9,51</t>
+          <t>3,37; 9,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,95</t>
+          <t>3,64; 8,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 9,46</t>
+          <t>4,52; 9,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,29</t>
+          <t>0,8; 6,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,35</t>
+          <t>1,78; 6,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,07</t>
+          <t>2,12; 7,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,13</t>
+          <t>0,67; 3,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,98</t>
+          <t>2,83; 6,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,75</t>
+          <t>3,34; 6,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,43</t>
+          <t>4,07; 8,01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,51</t>
+          <t>2,08; 3,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,07</t>
+          <t>5,64; 7,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 6,29</t>
+          <t>4,31; 6,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 7,81</t>
+          <t>5,4; 8,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,55</t>
+          <t>0,8; 2,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,29</t>
+          <t>1,31; 3,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,41</t>
+          <t>2,36; 4,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,66</t>
+          <t>2,48; 5,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,0</t>
+          <t>1,8; 2,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,07</t>
+          <t>4,38; 6,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 5,35</t>
+          <t>3,76; 5,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,85</t>
+          <t>4,56; 6,51</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>888</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19859</t>
+          <t>21921</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8145; 23508</t>
+          <t>7516; 23863</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21491; 45405</t>
+          <t>20249; 44651</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11344; 29892</t>
+          <t>11224; 30323</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12188; 29012</t>
+          <t>13894; 31098</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 11058</t>
+          <t>0; 10831</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>991; 8976</t>
+          <t>0; 8262</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5482</t>
+          <t>0; 4794</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2935</t>
+          <t>0; 3079</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9691; 28513</t>
+          <t>10445; 29381</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23598; 49226</t>
+          <t>24658; 49168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12455; 31297</t>
+          <t>12828; 31273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13190; 30354</t>
+          <t>14660; 31917</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56661</t>
+          <t>63311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71132</t>
+          <t>81940</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20836; 41199</t>
+          <t>20821; 41867</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68732; 106096</t>
+          <t>67975; 106587</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49918; 82047</t>
+          <t>49574; 80671</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40980; 79643</t>
+          <t>47264; 86313</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4772; 17439</t>
+          <t>3961; 16207</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7736; 23116</t>
+          <t>7883; 23961</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17883; 39007</t>
+          <t>17108; 39048</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5684; 26820</t>
+          <t>11268; 30524</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27851; 52465</t>
+          <t>27891; 53103</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82774; 122306</t>
+          <t>81616; 121080</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72668; 110002</t>
+          <t>70537; 109979</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47026; 96203</t>
+          <t>61631; 102263</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22069</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>36571</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3060; 16371</t>
+          <t>3099; 17041</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11343; 31021</t>
+          <t>11006; 31049</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13500; 33963</t>
+          <t>13826; 34075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14368; 32574</t>
+          <t>16643; 36629</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5321</t>
+          <t>0; 4752</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1795; 14120</t>
+          <t>1790; 13687</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4768; 17909</t>
+          <t>5027; 19200</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4804; 17414</t>
+          <t>5729; 21301</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3537; 17042</t>
+          <t>3655; 17207</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15840; 38443</t>
+          <t>15598; 38366</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21240; 44682</t>
+          <t>22078; 45119</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21596; 43881</t>
+          <t>25936; 51061</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>109186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>31247</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>122222</t>
+          <t>140433</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38924; 66093</t>
+          <t>39033; 67920</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>116677; 164265</t>
+          <t>114752; 162529</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84063; 125061</t>
+          <t>85698; 127442</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78868; 122793</t>
+          <t>90313; 137829</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7108; 22856</t>
+          <t>7166; 22250</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13863; 34593</t>
+          <t>13739; 35819</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26133; 50483</t>
+          <t>26972; 50975</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12351; 37393</t>
+          <t>22445; 47793</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50788; 83364</t>
+          <t>49996; 81576</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>135743; 187385</t>
+          <t>135132; 187268</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>120345; 167765</t>
+          <t>117982; 167400</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>90399; 151778</t>
+          <t>117462; 167768</t>
         </is>
       </c>
     </row>
